--- a/real_estate_forms/027_real_estate_license_extension_form--real_estate_forms.xlsx
+++ b/real_estate_forms/027_real_estate_license_extension_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form</t>
+          <t>real_estate_license_extension_form_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form</t>
+          <t>Real Estate License Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_real_estate_license_status</t>
+          <t>real_estate_license_extension_form_license_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>real_estate_license_status</t>
+          <t>Real Estate License Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_real_estate_license_type</t>
+          <t>real_estate_license_extension_form_license_number</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>real_estate_license_type</t>
+          <t>Real Estate License Number</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_real_estate_license_number</t>
+          <t>real_estate_license_extension_form_license_renewal_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>real_estate_license_number</t>
+          <t>License Renewal Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_renewal_date</t>
+          <t>real_estate_license_extension_form_license_expiration_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>license_renewal_date</t>
+          <t>License Expiration Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_expiration_date</t>
+          <t>real_estate_license_extension_form_license_expiration_date_certification</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>license_expiration_date</t>
+          <t>License Expiration Date Certification</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_expiration_date_certification</t>
+          <t>real_estate_license_extension_form_renewal_fee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>license_expiration_date_certification</t>
+          <t>Renewal Fee</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_renewal_fee</t>
+          <t>real_estate_license_extension_form_renewal_fee_currency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>renewal_fee</t>
+          <t>Renewal Fee Currency</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_renewal_fee_currency</t>
+          <t>real_estate_license_extension_form_renewal_fee_other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>renewal_fee_currency</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Real Estate License Extension Form Renewal Fee Currency Other</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_renewal_fee_other</t>
+          <t>real_estate_license_extension_form_licensed_since</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Licensed Since</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_licensed_since</t>
+          <t>real_estate_license_extension_form_license_expiration_date_extension</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>licensed_since</t>
+          <t>License Expiration Date Extension</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_expiration_date_extension</t>
+          <t>real_estate_license_extension_form_extension_period</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>license_expiration_date_extension</t>
+          <t>Extension Period</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_extension_period</t>
+          <t>real_estate_license_extension_form_license_renewal_status</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>extension_period</t>
+          <t>License Renewal Status</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_renewal_status</t>
+          <t>real_estate_license_extension_form_license_status_extension</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>license_renewal_status</t>
+          <t>License Status After Extension</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_submit</t>
+          <t>real_estate_license_extension_form_renewal_type</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Renewal Type</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_status_extension</t>
+          <t>real_estate_license_extension_form_renewal_fee_amount</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>license_status_extension</t>
+          <t>Renewal Fee Amount</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_extension_status</t>
+          <t>real_estate_license_extension_form_license_expiration_date_extension_certification</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>extension_status</t>
+          <t>License Expiration Date Extension Certification</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_renewal_type</t>
+          <t>real_estate_license_extension_form_renewal_fee_currency_certification</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>renewal_type</t>
+          <t>Renewal Fee Currency Certification</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_renewal_fee_amount</t>
+          <t>real_estate_license_extension_form_renewal_fee_other_certification</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>renewal_fee_amount</t>
+          <t>Real Estate License Extension Form Renewal Fee Other Certification</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,113 +975,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_expiration_date_extension_certification</t>
+          <t>real_estate_license_extension_form_submit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>license_expiration_date_extension_certification</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>real_estate_license_extension_form_renewal_fee_currency_certification</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>renewal_fee_currency_certification</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>real_estate_license_extension_form_renewal_fee_other_certification</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>real_estate_license_extension_form_renewal_fee_other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>real_estate_license_extension_form_submit_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit_2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1034,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_real_estate_license_status_choices</t>
+          <t>real_estate_license_extension_form_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1051,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_real_estate_license_status_choices</t>
+          <t>real_estate_license_extension_form_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,34 +1068,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_real_estate_license_type_choices</t>
+          <t>real_estate_license_extension_form_license_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_real_estate_license_type_choices</t>
+          <t>real_estate_license_extension_form_license_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1364,136 +1272,102 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_extension_status_choices</t>
+          <t>real_estate_license_extension_form_renewal_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_extension_status_choices</t>
+          <t>real_estate_license_extension_form_renewal_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_renewal_type_choices</t>
+          <t>real_estate_license_extension_form_license_expiration_date_extension_certification_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_renewal_type_choices</t>
+          <t>real_estate_license_extension_form_license_expiration_date_extension_certification_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_expiration_date_extension_certification_choices</t>
+          <t>real_estate_license_extension_form_renewal_fee_currency_certification_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>real_estate_license_extension_form_license_expiration_date_extension_certification_choices</t>
+          <t>real_estate_license_extension_form_renewal_fee_currency_certification_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>real_estate_license_extension_form_renewal_fee_currency_certification_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>real_estate_license_extension_form_renewal_fee_currency_certification_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
